--- a/Output/SelCountries/SelectStats.xlsx
+++ b/Output/SelCountries/SelectStats.xlsx
@@ -478,7 +478,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n" s="2">
-        <v>45762.800473289615</v>
+        <v>46097.893952496815</v>
       </c>
     </row>
   </sheetData>
@@ -1115,52 +1115,52 @@
         <v>2.0</v>
       </c>
       <c r="O3" t="n">
-        <v>-78.00516260318527</v>
+        <v>274.84522073612345</v>
       </c>
       <c r="P3" t="n">
-        <v>0.06746883092601755</v>
+        <v>-0.13368115832244634</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2028848428057305</v>
+        <v>2.14726392336208</v>
       </c>
       <c r="R3" t="n">
-        <v>0.06909565710236987</v>
+        <v>-2.1404597015322153</v>
       </c>
       <c r="S3"/>
       <c r="T3" t="n">
-        <v>152.5989744967096</v>
+        <v>3.4518211104548624</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08729884164321362</v>
+        <v>0.0018735039196184407</v>
       </c>
       <c r="V3" t="n">
-        <v>0.08735199289684759</v>
+        <v>2.228533503024127</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0062374345960988925</v>
+        <v>2.2285468060091342</v>
       </c>
       <c r="X3"/>
       <c r="Y3" t="n">
-        <v>1756.0017383309662</v>
+        <v>1943.6673123444054</v>
       </c>
       <c r="Z3" t="n">
-        <v>1915.9996941105298</v>
+        <v>1945.9999854197115</v>
       </c>
       <c r="AA3"/>
       <c r="AB3"/>
       <c r="AC3" t="n">
-        <v>4.268077655700429</v>
+        <v>1.0132693679674891</v>
       </c>
       <c r="AD3" t="n">
-        <v>6.350616103863608</v>
+        <v>1.6544442884557882</v>
       </c>
       <c r="AE3"/>
       <c r="AF3"/>
       <c r="AG3" t="n">
-        <v>43.1</v>
+        <v>16.13</v>
       </c>
       <c r="AH3" t="n">
-        <v>9.53</v>
+        <v>20.9</v>
       </c>
       <c r="AI3"/>
       <c r="AJ3"/>
@@ -1178,21 +1178,23 @@
       </c>
       <c r="AO3"/>
       <c r="AP3" t="n">
-        <v>1796.3974176168006</v>
+        <v>1794.158756147247</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1833.3206730767338</v>
+        <v>1831.5611849019388</v>
       </c>
       <c r="AR3" t="n">
-        <v>1870.243928536667</v>
+        <v>1868.96361365663</v>
       </c>
       <c r="AS3" t="n">
-        <v>1907.1671839966002</v>
+        <v>1906.3660424113218</v>
       </c>
       <c r="AT3" t="n">
-        <v>1973.356695867462</v>
-      </c>
-      <c r="AU3"/>
+        <v>1983.126932677228</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2022.5351981841145</v>
+      </c>
       <c r="AV3"/>
       <c r="AW3" t="n">
         <v>10.299999999999997</v>
@@ -1228,7 +1230,7 @@
         <v>2023.0</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0.13541601187971294</v>
+        <v>-0.13368115832244634</v>
       </c>
       <c r="BI3" t="s">
         <v>131</v>
@@ -1534,44 +1536,44 @@
         <v>2.0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-6.817747217086978</v>
+        <v>-6.817747345023488</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.018180856685986863</v>
+        <v>0.01818085675563746</v>
       </c>
       <c r="BS4" t="n">
-        <v>-0.3021628522321248</v>
+        <v>-0.30216285218914585</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.27260154974777695</v>
+        <v>0.27260154964382277</v>
       </c>
       <c r="BU4"/>
       <c r="BV4" t="n">
-        <v>19.310340025472996</v>
+        <v>19.310340025472954</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.010454500652445653</v>
+        <v>0.01045450065244563</v>
       </c>
       <c r="BX4" t="n">
         <v>0.016335757490612942</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.013803868172391718</v>
+        <v>0.01380386817239171</v>
       </c>
       <c r="BZ4"/>
       <c r="CA4" t="n">
-        <v>1877.4740648606871</v>
+        <v>1877.4740648393094</v>
       </c>
       <c r="CB4" t="n">
-        <v>1931.3473206424558</v>
+        <v>1931.3473206533672</v>
       </c>
       <c r="CC4"/>
       <c r="CD4"/>
       <c r="CE4" t="n">
-        <v>1.778325851346241</v>
+        <v>1.7783258517213016</v>
       </c>
       <c r="CF4" t="n">
-        <v>1.8243158164347242</v>
+        <v>1.8243158173463956</v>
       </c>
       <c r="CG4"/>
       <c r="CH4"/>
@@ -1599,18 +1601,18 @@
       <c r="CR4"/>
       <c r="CS4"/>
       <c r="CT4" t="n">
-        <v>1885.6307076201963</v>
+        <v>1885.6307076106527</v>
       </c>
       <c r="CU4" t="n">
-        <v>1903.2374576199077</v>
+        <v>1903.237457617347</v>
       </c>
       <c r="CV4" t="n">
-        <v>1920.844207619619</v>
+        <v>1920.8442076240412</v>
       </c>
       <c r="CW4"/>
       <c r="CX4"/>
       <c r="CY4" t="n">
-        <v>-0.28398199554613796</v>
+        <v>-0.2839819954335084</v>
       </c>
     </row>
     <row r="5">
@@ -1904,63 +1906,63 @@
         <v>3.0</v>
       </c>
       <c r="O6" t="n">
-        <v>-201.57926873858224</v>
+        <v>-282.15256903019707</v>
       </c>
       <c r="P6" t="n">
-        <v>0.12659935901345892</v>
+        <v>0.16936758885870234</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.17658912509169425</v>
+        <v>-0.3575267008721853</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.3270575335005412</v>
+        <v>1.0156803277364252</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.11207159853531434</v>
+        <v>-1.2862782960284356</v>
       </c>
       <c r="T6" t="n">
-        <v>291.345364090494</v>
+        <v>87.660484642091</v>
       </c>
       <c r="U6" t="n">
-        <v>0.15451853526369877</v>
+        <v>0.0463809231534349</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1550382531181254</v>
+        <v>0.04901963929258954</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0622488808868416</v>
+        <v>0.1632166231421831</v>
       </c>
       <c r="X6" t="n">
-        <v>0.07683929231204696</v>
+        <v>0.16273622785362996</v>
       </c>
       <c r="Y6" t="n">
-        <v>1892.9998828312275</v>
+        <v>1901.168906354905</v>
       </c>
       <c r="Z6" t="n">
-        <v>1966.98724754928</v>
+        <v>1948.163037846622</v>
       </c>
       <c r="AA6" t="n">
-        <v>1992.9269652256453</v>
+        <v>1958.6927018835906</v>
       </c>
       <c r="AB6"/>
       <c r="AC6" t="n">
-        <v>8.045861244507124</v>
+        <v>2.0786129985107227</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.1920573665709733</v>
+        <v>1.0561433501068358</v>
       </c>
       <c r="AE6" t="n">
-        <v>11.113635359326935</v>
+        <v>0.8011875618928814</v>
       </c>
       <c r="AF6"/>
       <c r="AG6" t="n">
-        <v>40.9</v>
+        <v>42.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>36.346</v>
+        <v>30.7</v>
       </c>
       <c r="AI6" t="n">
-        <v>26.209</v>
+        <v>39.743</v>
       </c>
       <c r="AJ6"/>
       <c r="AK6" t="n">
@@ -1977,23 +1979,21 @@
       </c>
       <c r="AO6"/>
       <c r="AP6" t="n">
-        <v>1954.4785269919985</v>
+        <v>1956.7387897286435</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1978.5897493847015</v>
+        <v>1979.8694235147857</v>
       </c>
       <c r="AR6" t="n">
-        <v>1991.8506850964434</v>
+        <v>1990.7684378617041</v>
       </c>
       <c r="AS6" t="n">
-        <v>2002.3197560202927</v>
+        <v>2001.6674522086228</v>
       </c>
       <c r="AT6" t="n">
-        <v>2012.542219350331</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2022.764682680369</v>
-      </c>
+        <v>2012.5664665555412</v>
+      </c>
+      <c r="AU6"/>
       <c r="AV6"/>
       <c r="AW6" t="n">
         <v>31.481</v>
@@ -2029,7 +2029,7 @@
         <v>2023.0</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.4891188981140908</v>
+        <v>-0.4587570803054932</v>
       </c>
       <c r="BI6" t="s">
         <v>131</v>
@@ -2412,13 +2412,13 @@
         <v>2.0</v>
       </c>
       <c r="I8" t="n">
-        <v>666.1523580742648</v>
+        <v>726.0421572758601</v>
       </c>
       <c r="J8" t="n">
-        <v>497.80018091422727</v>
+        <v>595.819368681973</v>
       </c>
       <c r="K8" t="n">
-        <v>423.8953847466833</v>
+        <v>498.67243686990315</v>
       </c>
       <c r="L8"/>
       <c r="M8"/>
@@ -2426,44 +2426,44 @@
         <v>2.0</v>
       </c>
       <c r="O8" t="n">
-        <v>-157.60536494896218</v>
+        <v>-157.60536603898345</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1035390026724203</v>
+        <v>0.10353900323966479</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3621104298170237</v>
+        <v>-1.3592743021009044</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7814982575299536</v>
+        <v>0.8648936707096972</v>
       </c>
       <c r="S8"/>
       <c r="T8" t="n">
-        <v>33.23830250582458</v>
+        <v>35.16596985805712</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01722523703115252</v>
+        <v>0.018224220870763492</v>
       </c>
       <c r="V8" t="n">
-        <v>0.10304074389596511</v>
+        <v>0.09922675231127936</v>
       </c>
       <c r="W8" t="n">
-        <v>0.10422504973386659</v>
+        <v>0.09894777945570465</v>
       </c>
       <c r="X8"/>
       <c r="Y8" t="n">
-        <v>1955.583789801325</v>
+        <v>1955.5731843351616</v>
       </c>
       <c r="Z8" t="n">
-        <v>1970.3582862447204</v>
+        <v>1971.9896809063025</v>
       </c>
       <c r="AA8"/>
       <c r="AB8"/>
       <c r="AC8" t="n">
-        <v>0.7423668101170943</v>
+        <v>0.7692343258203417</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.3072278104170998</v>
+        <v>1.2275036648934092</v>
       </c>
       <c r="AE8"/>
       <c r="AF8"/>
@@ -2471,7 +2471,7 @@
         <v>44.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>27.2</v>
+        <v>24.2</v>
       </c>
       <c r="AI8"/>
       <c r="AJ8"/>
@@ -2479,34 +2479,36 @@
         <v>40.0</v>
       </c>
       <c r="AL8" t="n">
-        <v>9.754545454545456</v>
+        <v>7.362727272727273</v>
       </c>
       <c r="AM8" t="n">
         <v>29.10909090909091</v>
       </c>
       <c r="AN8" t="n">
-        <v>5.999999999999999</v>
+        <v>7.678455090757774</v>
       </c>
       <c r="AO8"/>
       <c r="AP8" t="n">
-        <v>1963.4290579175897</v>
+        <v>1963.4352968665603</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1967.4018161513784</v>
+        <v>1967.4170277333553</v>
       </c>
       <c r="AR8" t="n">
-        <v>1973.0393659967956</v>
+        <v>1971.4016129942065</v>
       </c>
       <c r="AS8" t="n">
-        <v>1983.5199386184727</v>
+        <v>1982.8840117415775</v>
       </c>
       <c r="AT8" t="n">
-        <v>1994.0005112401498</v>
+        <v>1995.6769172047116</v>
       </c>
       <c r="AU8" t="n">
-        <v>2004.481083861827</v>
-      </c>
-      <c r="AV8"/>
+        <v>2008.4698226678454</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2021.2627281309792</v>
+      </c>
       <c r="AW8" t="n">
         <v>38.4</v>
       </c>
@@ -2514,10 +2516,10 @@
         <v>1951.0</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.9000000000000004</v>
+        <v>-2.990000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2010.0</v>
+        <v>2023.0</v>
       </c>
       <c r="BA8" t="n">
         <v>14.0</v>
@@ -2529,19 +2531,19 @@
         <v>33.0</v>
       </c>
       <c r="BD8" t="n">
-        <v>25.0</v>
+        <v>31.0</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="BF8" t="n">
         <v>1906.0</v>
       </c>
       <c r="BG8" t="n">
-        <v>2010.0</v>
+        <v>2024.0</v>
       </c>
       <c r="BH8" t="n">
-        <v>-1.2585714271446033</v>
+        <v>-1.2557352988612396</v>
       </c>
       <c r="BI8" t="s">
         <v>131</v>
@@ -2550,13 +2552,13 @@
         <v>3.0</v>
       </c>
       <c r="BK8" t="n">
-        <v>582.780438851573</v>
+        <v>685.1941924745438</v>
       </c>
       <c r="BL8" t="n">
-        <v>409.7557468900122</v>
+        <v>444.3601919780753</v>
       </c>
       <c r="BM8" t="n">
-        <v>406.74389744779853</v>
+        <v>442.72065949882756</v>
       </c>
       <c r="BN8"/>
       <c r="BO8"/>
@@ -2564,99 +2566,99 @@
         <v>3.0</v>
       </c>
       <c r="BQ8" t="n">
-        <v>759.3714190130478</v>
+        <v>759.3851508584806</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0.3819848660007992</v>
+        <v>-0.38199202109434865</v>
       </c>
       <c r="BS8" t="n">
-        <v>-0.7213904959551065</v>
+        <v>-0.7218432312072262</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.8732846046353336</v>
+        <v>0.908786293415211</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.27603600772994147</v>
+        <v>0.2713013695098145</v>
       </c>
       <c r="BV8" t="n">
-        <v>40.32427069699927</v>
+        <v>38.796887545866426</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.020946469189552258</v>
+        <v>0.020153068997488123</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.35689064747748217</v>
+        <v>0.3433725167752555</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.3626526345383343</v>
+        <v>0.34615118749196866</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.07095359175884706</v>
+        <v>0.05044015786006428</v>
       </c>
       <c r="CA8" t="n">
-        <v>1947.000390606384</v>
+        <v>1947.000508646377</v>
       </c>
       <c r="CB8" t="n">
-        <v>1953.4132737436282</v>
+        <v>1953.6722472749382</v>
       </c>
       <c r="CC8" t="n">
-        <v>1971.4615025962944</v>
+        <v>1975.1309171951796</v>
       </c>
       <c r="CD8"/>
       <c r="CE8" t="n">
-        <v>2.0526375360395637</v>
+        <v>1.973603914939039</v>
       </c>
       <c r="CF8" t="n">
-        <v>1.5988331518833823</v>
+        <v>1.5130844987528802</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.074437958145038</v>
+        <v>2.6802621593828238</v>
       </c>
       <c r="CH8"/>
       <c r="CI8" t="n">
         <v>18.1</v>
       </c>
       <c r="CJ8" t="n">
-        <v>9.4</v>
+        <v>8.2</v>
       </c>
       <c r="CK8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="CL8"/>
       <c r="CM8" t="n">
         <v>40.0</v>
       </c>
       <c r="CN8" t="n">
-        <v>9.754545454545456</v>
+        <v>7.362727272727273</v>
       </c>
       <c r="CO8" t="n">
         <v>29.10909090909091</v>
       </c>
       <c r="CP8" t="n">
-        <v>5.999999999999999</v>
+        <v>7.678455090757774</v>
       </c>
       <c r="CQ8"/>
       <c r="CR8"/>
       <c r="CS8" t="n">
-        <v>1909.4249116443314</v>
+        <v>1909.425094191506</v>
       </c>
       <c r="CT8" t="n">
-        <v>1922.5144354580564</v>
+        <v>1922.514372825326</v>
       </c>
       <c r="CU8" t="n">
-        <v>1935.6039592717814</v>
+        <v>1935.603651459146</v>
       </c>
       <c r="CV8" t="n">
-        <v>1947.586427951279</v>
+        <v>1947.5860484721043</v>
       </c>
       <c r="CW8" t="n">
-        <v>1952.118083005963</v>
+        <v>1952.115847622146</v>
       </c>
       <c r="CX8" t="n">
-        <v>1984.1246655738464</v>
+        <v>1986.979723325556</v>
       </c>
       <c r="CY8" t="n">
-        <v>-1.1033753619559057</v>
+        <v>-1.1038352523015749</v>
       </c>
     </row>
     <row r="9">
